--- a/data/trans_dic/P33B_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P33B_R3-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 12,68</t>
+          <t>3,49; 12,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 8,63</t>
+          <t>2,5; 10,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,58</t>
+          <t>3,83; 9,68</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 9,91</t>
+          <t>3,28; 9,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,74</t>
+          <t>7,98; 13,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 10,21</t>
+          <t>6,42; 10,42</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,83%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,28; 17,95</t>
+          <t>10,84; 16,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,54</t>
+          <t>11,89; 16,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 16,24</t>
+          <t>12,1; 15,88</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,96</t>
+          <t>14,12; 19,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 24,33</t>
+          <t>19,62; 24,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,19; 20,1</t>
+          <t>17,83; 21,44</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,82; 20,42</t>
+          <t>14,3; 20,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,27; 33,69</t>
+          <t>27,9; 33,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21,97; 26,16</t>
+          <t>22,09; 26,24</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,75; 23,53</t>
+          <t>17,15; 23,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 32,35</t>
+          <t>28,26; 34,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 26,48</t>
+          <t>23,81; 28,52</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>27,72; 36,43</t>
+          <t>28,02; 36,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,95; 39,6</t>
+          <t>33,9; 40,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,17; 37,48</t>
+          <t>32,35; 37,89</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,43; 16,15</t>
+          <t>14,23; 16,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,55; 21,85</t>
+          <t>20,84; 23,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 18,71</t>
+          <t>18,03; 19,66</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25904</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39536</t>
+          <t>48476</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11821; 50723</t>
+          <t>14227; 52163</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5836; 27019</t>
+          <t>9045; 36955</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23068; 68290</t>
+          <t>29510; 74584</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>26959</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47721</t>
+          <t>52941</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73529</t>
+          <t>79900</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15830; 41959</t>
+          <t>15619; 43084</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29017; 65183</t>
+          <t>39982; 67769</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>53346; 95441</t>
+          <t>62822; 101927</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>77608</t>
+          <t>83974</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>74842</t>
+          <t>87754</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>152451</t>
+          <t>171727</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>60415; 96097</t>
+          <t>67213; 104429</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>61816; 89707</t>
+          <t>73979; 104055</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>131329; 175080</t>
+          <t>150251; 197217</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>107558</t>
+          <t>117464</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>153003</t>
+          <t>165057</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260560</t>
+          <t>282522</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>50014; 159441</t>
+          <t>98962; 139678</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>127575; 173330</t>
+          <t>144520; 181327</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163098; 321693</t>
+          <t>256190; 308057</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>98440</t>
+          <t>104447</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>166306</t>
+          <t>187410</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264746</t>
+          <t>291857</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>83019; 114381</t>
+          <t>87011; 122480</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148788; 183787</t>
+          <t>169685; 205124</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>242930; 289320</t>
+          <t>268667; 319215</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>74275</t>
+          <t>83095</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>124585</t>
+          <t>137771</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>198861</t>
+          <t>220866</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61658; 86642</t>
+          <t>69816; 96583</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55990; 196833</t>
+          <t>124107; 152721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>106228; 258609</t>
+          <t>201512; 241388</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>90737</t>
+          <t>100168</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>154409</t>
+          <t>172019</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245146</t>
+          <t>272187</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>78373; 103009</t>
+          <t>86931; 114320</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140294; 168624</t>
+          <t>157483; 189203</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>227985; 265608</t>
+          <t>250685; 293538</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>500330</t>
+          <t>545433</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>734497</t>
+          <t>822101</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1234827</t>
+          <t>1367535</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>395284; 558367</t>
+          <t>502273; 593798</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>605619; 799633</t>
+          <t>778040; 864171</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1074122; 1331942</t>
+          <t>1309728; 1428418</t>
         </is>
       </c>
     </row>
